--- a/daily_matches/job_matches_2026-08-22.xlsx
+++ b/daily_matches/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Scientist, Business Ventures</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>UNITED STATES SOCCER FEDERATION 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Generative AI, RAG, XGBoost, S3, EC2, Redshift, BigQuery, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9ede359be55ea6d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc46eb12376a92e8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, S3, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bc68670e06fc48</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10850 – Sr. Software Engineer, Applied AI</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, LLaMA, Hugging Face, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
+          <t>Data Scientist, Generative AI, RAG, Cortex, Docker, Kubernetes, Apache Airflow, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f4c04ef00a4ce91</t>
+          <t>https://www.indeed.com/viewjob?jk=48397f4e7a2d566c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kinesis, Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, Polars, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kinesis, Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, Polars, Python, SQL</t>
+          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git, BigQuery, Kafka, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
+          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Automation Quality Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Git, Snowflake, BigQuery, Redshift, Kafka, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191eecfc2d526c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer - Dealer Network &amp; Employee Engagement</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Terraform, Git, Kafka, PostgreSQL, Cassandra, NoSQL, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, BigQuery, Snowflake, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f2ec2162bd8ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da10929e7b86d9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Senior Software Engineer, AI (New York)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=ef81863247e7e6a6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Cloud Agentic AI Platform Engineer / Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, MongoDB, Python, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c009d6a6ced35c81</t>
+          <t>https://www.indeed.com/viewjob?jk=748b4fc220811141</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Canopy Tax</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fa5158342fbcfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=b45e9122fd96fa7f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Scientific Data Engineer</t>
+          <t>Software Engineer - Dealer Network &amp; Employee Engagement</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lawrence Berkeley National Laboratory</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, Docker, Terraform, Git, Kafka, PostgreSQL, Cassandra, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f855437b0a9b49f6</t>
+          <t>https://www.indeed.com/viewjob?jk=0bcaf2b4ad066304</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Terraform, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=bcbda851b87fa1a2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Terraform, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e3b7d01376f88b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps/SRE Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d95e088d2442d91</t>
+          <t>https://www.indeed.com/viewjob?jk=030efd6e5fbd7469</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevOps/SRE Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plymouth Meeting, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a80129a13b74194</t>
+          <t>https://www.indeed.com/viewjob?jk=f32f3f71cc37d5e1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior DevOps/SRE Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CREDIT GENIE</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e48bf604c2f8ff</t>
+          <t>https://www.indeed.com/viewjob?jk=257a1eaced5a7ac1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mid-Level Observability Engineer (Job ID 3021798)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a16b04d6d733b301</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef58c3212bcaf8d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Sr Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Kafka, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
+          <t>https://www.indeed.com/viewjob?jk=eaeceb6db608bdd2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Junior Data Engineer - ETL Development</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec46dc517eaed4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=fba0ae80747812b9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Junior Data Engineer - ETL Development</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ca9add1f6d36bca</t>
+          <t>https://www.indeed.com/viewjob?jk=867a808a38849f20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Junior Data Engineer - ETL Development</t>
+          <t>Senior Data Scientist - Forecasting</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, AWS SageMaker, GCP Vertex AI, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d00d564fd7d0aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=73467e7d334ac311</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Visualization Professional - Power BI</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Direct Supply</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Dataflow, Git, Tableau, Power BI, MicroStrategy, R</t>
+          <t>AI Engineer, LangChain, RAG, Hugging Face, Docker, Kubernetes, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a4d5d6ee29a460</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf28d4f3f647ea1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Application Development Engineer</t>
+          <t>Forward-Deployed Engineer (FDE), Strategic Accounts</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Deepgram</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>Prompt Engineering, Docker, Kubernetes, AKS, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817908e443592c1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f74e9312ceae880</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Junior Data Engineer - ETL Development</t>
+          <t>ML/AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94af144a70b5efa4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a695d757fc6dc5b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Junior Data Engineer - ETL Development</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PowerSchool Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbc11eb51cc6376a</t>
+          <t>https://www.indeed.com/viewjob?jk=715bad83508e40d2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Junior Data Engineer - ETL Development</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PowerSchool Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81f719d0e558dc3d</t>
+          <t>https://www.indeed.com/viewjob?jk=263bf1ca0501b215</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Visualization Professional - Power BI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PowerSchool Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Dataflow, Git, Tableau, Power BI, MicroStrategy, R</t>
+          <t>Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63b004ade230783</t>
+          <t>https://www.indeed.com/viewjob?jk=92f6ef0186d11e9a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Consultant, AI Software Engineering</t>
+          <t>Billing Operations Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FI Consulting</t>
+          <t>Advyzon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, S3, CI/CD, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe4dd245f5918d91</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7bb7b0b9d70467</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Developer II - Information Services (Full-Time, Exempt)</t>
+          <t>Associate, Application Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Enloe Medical Center</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chico, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>RAG, CI/CD, Kafka, Cassandra, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b854402617b05ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdc80289d2c74a1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Java &amp; AWS Software Engineer III</t>
+          <t>Machine Learning Scientist III - Ads + Search &amp; Recommendations</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, BigQuery, MLflow, Docker, BigQuery, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490254591339acf6</t>
+          <t>https://www.indeed.com/viewjob?jk=d04beed2c04978ba</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Data Scientist - Senior Associate</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Snowflake, Tableau, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791cb17a514682ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PathLabs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,42 +1581,2947 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cbeea95e71d8d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MTS 2, Software Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Williamsville, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>Austin, TX, US USA</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Data Lake, Docker, Git, Kafka, Hadoop, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa7a5baf77657127</t>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>San Juan, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Rosslyn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Honolulu, HI, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Monterey, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Lansing, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Cyber - AWS Forward Deployed Security Engineer (FDE) - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1aa8d9cc61d51743</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Cyber - AWS Forward Deployed Security Engineer (FDE) - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c9501a8360dd713</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Cyber - AWS Forward Deployed Security Engineer (FDE) - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bde42a5e3a2e4838</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Cyber - AWS Forward Deployed Security Engineer (FDE) - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb7615bd26465c6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Cyber - AWS Forward Deployed Security Engineer (FDE) - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22b4647af40956b2</t>
         </is>
       </c>
     </row>
